--- a/5_Judgemental_Forecasts_Derivations_Analysis/0_Main/AR2/0_EDA_Tables/Summary_Statistics_h4.xlsx
+++ b/5_Judgemental_Forecasts_Derivations_Analysis/0_Main/AR2/0_EDA_Tables/Summary_Statistics_h4.xlsx
@@ -480,34 +480,34 @@
         <v>15</v>
       </c>
       <c r="C2">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="D2">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="E2">
         <v>0.9593</v>
       </c>
       <c r="F2">
-        <v>0.9401</v>
+        <v>1.0079</v>
       </c>
       <c r="G2">
-        <v>-0.0192</v>
+        <v>0.0486</v>
       </c>
       <c r="H2">
-        <v>-0.0948</v>
+        <v>0.7911</v>
       </c>
       <c r="I2">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="J2">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="K2">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="L2">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="M2">
         <v>48</v>
@@ -524,37 +524,37 @@
         <v>16</v>
       </c>
       <c r="C3">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3">
-        <v>0.831</v>
+        <v>1.1509</v>
       </c>
       <c r="F3">
-        <v>0.802</v>
+        <v>0.9709</v>
       </c>
       <c r="G3">
-        <v>-0.029</v>
+        <v>-0.1801</v>
       </c>
       <c r="H3">
-        <v>-0.0596</v>
+        <v>-0.4032</v>
       </c>
       <c r="I3">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="J3">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="K3">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="L3">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="M3">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="N3">
         <v>4</v>
@@ -571,34 +571,34 @@
         <v>0</v>
       </c>
       <c r="D4">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="E4">
-        <v>1.6007</v>
+        <v>0.7129</v>
       </c>
       <c r="F4">
-        <v>1.6305</v>
+        <v>1.0556</v>
       </c>
       <c r="G4">
-        <v>0.0298</v>
+        <v>0.3427</v>
       </c>
       <c r="H4">
-        <v>-0.2705</v>
+        <v>2.3266</v>
       </c>
       <c r="I4">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J4">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="K4">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="L4">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M4">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="N4">
         <v>4</v>
